--- a/OCT_2026/10-14-26/Zeshan.xlsx
+++ b/OCT_2026/10-14-26/Zeshan.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D564C8F-4067-439A-A2EC-201DE2ED8E33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D3BE852-D84E-4ECA-97EB-3B016FF53AA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="948" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8517,7 +8517,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="88" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="10" orientation="landscape" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -9939,7 +9939,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="88" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="10" orientation="landscape" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -11361,7 +11361,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="88" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="10" orientation="landscape" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -12783,7 +12783,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="88" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="10" orientation="landscape" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -14205,7 +14205,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="88" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="10" orientation="landscape" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -15631,7 +15631,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="88" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="10" orientation="landscape" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -47885,7 +47885,7 @@
       <c r="L4" s="395"/>
       <c r="M4" s="398">
         <f ca="1">TODAY()+1</f>
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="N4" s="398"/>
       <c r="O4" s="398"/>
@@ -47913,7 +47913,7 @@
       <c r="L5" s="395"/>
       <c r="M5" s="398">
         <f ca="1">M4-1</f>
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="N5" s="394"/>
       <c r="O5" s="394"/>
@@ -54352,7 +54352,7 @@
       </c>
       <c r="T7" s="301">
         <f>+'5'!P35</f>
-        <v>17074.94950601695</v>
+        <v>20211.161091101694</v>
       </c>
       <c r="XEX7" t="s">
         <v>107</v>
@@ -54711,19 +54711,19 @@
       </c>
       <c r="H12" s="309">
         <f>+'1'!H21+'2'!H21+'3'!H21+'4'!H21+'5'!H21+'6'!H21+'7'!H21+'8'!H21+'9'!H21+'10'!H21+'11'!H21+'12'!H21+'13'!H21+'14'!H21+'15'!H21+'16'!H21+'17'!H21+'18'!H21+'19'!H21+'20'!H21+'21'!H21+'22'!H21+'23'!H21+'24'!H21+'25'!H21+'26'!H21+'27'!H21+'28'!H21+'29'!H21+'30'!H21</f>
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="I12" s="236">
         <f t="shared" si="0"/>
-        <v>2905.6</v>
+        <v>5811.2</v>
       </c>
       <c r="J12" s="286">
         <f>+'1'!J21+'2'!J21+'3'!J21+'4'!J21+'5'!J21+'6'!J21+'7'!J21+'8'!J21+'9'!J21+'10'!J21+'11'!J21+'12'!J21+'13'!J21+'14'!J21+'15'!J21+'16'!J21+'17'!J21+'18'!J21+'19'!J21+'20'!J21+'21'!J21+'22'!J21+'23'!J21+'24'!J21+'25'!J21+'26'!J21+'27'!J21+'28'!J21+'29'!J21+'30'!J21</f>
-        <v>232.44800000000001</v>
+        <v>464.89600000000002</v>
       </c>
       <c r="K12" s="286">
         <f>+'1'!K21+'2'!K21+'3'!K21+'4'!K21+'5'!K21+'6'!K21+'7'!K21+'8'!K21+'9'!K21+'10'!K21+'11'!K21+'12'!K21+'13'!K21+'14'!K21+'15'!K21+'16'!K21+'17'!K21+'18'!K21+'19'!K21+'20'!K21+'21'!K21+'22'!K21+'23'!K21+'24'!K21+'25'!K21+'26'!K21+'27'!K21+'28'!K21+'29'!K21+'30'!K21</f>
-        <v>101.69600000000001</v>
+        <v>203.39200000000002</v>
       </c>
       <c r="L12" s="286">
         <f>+'1'!L21+'2'!L21+'3'!L21+'4'!L21+'5'!L21+'6'!L21+'7'!L21+'8'!L21+'9'!L21+'10'!L21+'11'!L21+'12'!L21+'13'!L21+'14'!L21+'15'!L21+'16'!L21+'17'!L21+'18'!L21+'19'!L21+'20'!L21+'21'!L21+'22'!L21+'23'!L21+'24'!L21+'25'!L21+'26'!L21+'27'!L21+'28'!L21+'29'!L21+'30'!L21</f>
@@ -54731,19 +54731,19 @@
       </c>
       <c r="M12" s="230">
         <f t="shared" si="1"/>
-        <v>2571.4560000000001</v>
+        <v>5142.9120000000003</v>
       </c>
       <c r="N12" s="286">
         <f>+'1'!N21+'2'!N21+'3'!N21+'4'!N21+'5'!N21+'6'!N21+'7'!N21+'8'!N21+'9'!N21+'10'!N21+'11'!N21+'12'!N21+'13'!N21+'14'!N21+'15'!N21+'16'!N21+'17'!N21+'18'!N21+'19'!N21+'20'!N21+'21'!N21+'22'!N21+'23'!N21+'24'!N21+'25'!N21+'26'!N21+'27'!N21+'28'!N21+'29'!N21+'30'!N21</f>
-        <v>549.15254237288138</v>
+        <v>1098.3050847457628</v>
       </c>
       <c r="O12" s="286">
         <f>+'1'!O21+'2'!O21+'3'!O21+'4'!O21+'5'!O21+'6'!O21+'7'!O21+'8'!O21+'9'!O21+'10'!O21+'11'!O21+'12'!O21+'13'!O21+'14'!O21+'15'!O21+'16'!O21+'17'!O21+'18'!O21+'19'!O21+'20'!O21+'21'!O21+'22'!O21+'23'!O21+'24'!O21+'25'!O21+'26'!O21+'27'!O21+'28'!O21+'29'!O21+'30'!O21</f>
-        <v>15.603042711864408</v>
+        <v>31.206085423728815</v>
       </c>
       <c r="P12" s="311">
         <f t="shared" si="2"/>
-        <v>3136.2115850847458</v>
+        <v>6272.4231701694916</v>
       </c>
       <c r="Q12" s="213">
         <f>+'1'!Q21+'2'!Q21+'3'!Q21+'4'!Q21+'5'!Q21+'6'!Q21+'7'!Q21+'8'!Q21+'9'!Q21+'10'!Q21+'11'!Q21+'12'!Q21+'13'!Q21+'14'!Q21+'15'!Q21+'16'!Q21+'17'!Q21+'18'!Q21+'19'!Q21+'20'!Q21+'21'!Q21+'22'!Q21+'23'!Q21+'24'!Q21+'25'!Q21+'26'!Q21+'27'!Q21+'28'!Q21+'29'!Q21+'30'!Q21</f>
@@ -55015,23 +55015,23 @@
       <c r="F16" s="358"/>
       <c r="G16" s="117">
         <f>H16/40</f>
-        <v>9.5</v>
+        <v>10.5</v>
       </c>
       <c r="H16" s="113">
         <f t="shared" ref="H16:M16" si="3">SUM(H7:H15)</f>
-        <v>380</v>
+        <v>420</v>
       </c>
       <c r="I16" s="114">
         <f t="shared" si="3"/>
-        <v>23567.699999999997</v>
+        <v>26473.3</v>
       </c>
       <c r="J16" s="274">
         <f>SUM(J7:J15)</f>
-        <v>1885.4160000000002</v>
+        <v>2117.864</v>
       </c>
       <c r="K16" s="275">
         <f t="shared" si="3"/>
-        <v>824.86950000000002</v>
+        <v>926.56550000000004</v>
       </c>
       <c r="L16" s="276">
         <f t="shared" si="3"/>
@@ -55039,19 +55039,19 @@
       </c>
       <c r="M16" s="232">
         <f t="shared" si="3"/>
-        <v>20857.414499999999</v>
+        <v>23428.870500000001</v>
       </c>
       <c r="N16" s="233">
         <f>SUM(N7:N15)</f>
-        <v>4454.2372881355923</v>
+        <v>5003.389830508474</v>
       </c>
       <c r="O16" s="101">
         <f>SUM(O7:O15)</f>
-        <v>126.55825894067797</v>
+        <v>142.16130165254239</v>
       </c>
       <c r="P16" s="113">
         <f>SUM(P7:P15)</f>
-        <v>25438.210047076267</v>
+        <v>28574.421632161015</v>
       </c>
       <c r="Q16" s="128">
         <f>SUM(Q7:Q15)</f>
@@ -55138,7 +55138,7 @@
       <c r="O19" s="369"/>
       <c r="P19" s="139">
         <f>I16</f>
-        <v>23567.699999999997</v>
+        <v>26473.3</v>
       </c>
       <c r="R19" s="299">
         <v>17</v>
@@ -55170,7 +55170,7 @@
       <c r="O20" s="371"/>
       <c r="P20" s="140">
         <f>+J16</f>
-        <v>1885.4160000000002</v>
+        <v>2117.864</v>
       </c>
       <c r="R20" s="299">
         <v>18</v>
@@ -55202,7 +55202,7 @@
       <c r="O21" s="371"/>
       <c r="P21" s="140">
         <f>+K16+L16</f>
-        <v>824.86950000000002</v>
+        <v>926.56550000000004</v>
       </c>
       <c r="R21" s="299">
         <v>19</v>
@@ -55235,7 +55235,7 @@
       <c r="O22" s="371"/>
       <c r="P22" s="140">
         <f>P19-P20-P21</f>
-        <v>20857.414499999995</v>
+        <v>23428.870499999997</v>
       </c>
       <c r="R22" s="299">
         <v>20</v>
@@ -55270,7 +55270,7 @@
       </c>
       <c r="P23" s="140">
         <f>+N16</f>
-        <v>4454.2372881355923</v>
+        <v>5003.389830508474</v>
       </c>
       <c r="R23" s="299">
         <v>21</v>
@@ -55303,7 +55303,7 @@
       <c r="O24" s="373"/>
       <c r="P24" s="140">
         <f>P22+P23</f>
-        <v>25311.651788135587</v>
+        <v>28432.26033050847</v>
       </c>
       <c r="R24" s="299">
         <v>22</v>
@@ -55339,7 +55339,7 @@
       </c>
       <c r="P25" s="140">
         <f>+O16</f>
-        <v>126.55825894067797</v>
+        <v>142.16130165254239</v>
       </c>
       <c r="R25" s="299">
         <v>23</v>
@@ -55360,7 +55360,7 @@
       <c r="O26" s="375"/>
       <c r="P26" s="297">
         <f>+P24+P25</f>
-        <v>25438.210047076263</v>
+        <v>28574.421632161011</v>
       </c>
       <c r="R26" s="299">
         <v>24</v>
@@ -55474,7 +55474,7 @@
       </c>
       <c r="T33" s="304">
         <f>SUM(T3:T32)</f>
-        <v>25438.210047076267</v>
+        <v>28574.421632161011</v>
       </c>
     </row>
     <row r="44" spans="2:20" x14ac:dyDescent="0.35">
@@ -58371,7 +58371,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="88" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="10" orientation="landscape" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -59793,7 +59793,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="88" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="10" orientation="landscape" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -61215,7 +61215,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="88" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="10" orientation="landscape" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -62039,19 +62039,19 @@
       </c>
       <c r="G21" s="287"/>
       <c r="H21" s="96">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="I21" s="236">
         <f t="shared" si="0"/>
-        <v>2905.6</v>
+        <v>5811.2</v>
       </c>
       <c r="J21" s="272">
         <f t="shared" si="1"/>
-        <v>232.44800000000001</v>
+        <v>464.89600000000002</v>
       </c>
       <c r="K21" s="128">
         <f t="shared" si="1"/>
-        <v>101.69600000000001</v>
+        <v>203.39200000000002</v>
       </c>
       <c r="L21" s="119">
         <f t="shared" si="1"/>
@@ -62059,19 +62059,19 @@
       </c>
       <c r="M21" s="230">
         <f t="shared" si="2"/>
-        <v>2571.4560000000001</v>
+        <v>5142.9120000000003</v>
       </c>
       <c r="N21" s="277">
         <f t="shared" si="3"/>
-        <v>549.15254237288138</v>
+        <v>1098.3050847457628</v>
       </c>
       <c r="O21" s="239">
         <f t="shared" si="4"/>
-        <v>15.603042711864408</v>
+        <v>31.206085423728815</v>
       </c>
       <c r="P21" s="119">
         <f t="shared" si="5"/>
-        <v>3136.2115850847458</v>
+        <v>6272.4231701694916</v>
       </c>
       <c r="Q21" s="319"/>
       <c r="S21" s="269">
@@ -62329,19 +62329,19 @@
       </c>
       <c r="H25" s="113">
         <f t="shared" si="7"/>
-        <v>240</v>
+        <v>280</v>
       </c>
       <c r="I25" s="114">
         <f t="shared" si="7"/>
-        <v>15819.400000000001</v>
+        <v>18725</v>
       </c>
       <c r="J25" s="274">
         <f>SUM(J16:J24)</f>
-        <v>1265.5520000000001</v>
+        <v>1498</v>
       </c>
       <c r="K25" s="275">
         <f t="shared" si="7"/>
-        <v>553.67900000000009</v>
+        <v>655.37500000000011</v>
       </c>
       <c r="L25" s="276">
         <f t="shared" si="7"/>
@@ -62349,19 +62349,19 @@
       </c>
       <c r="M25" s="232">
         <f t="shared" si="7"/>
-        <v>14000.169000000002</v>
+        <v>16571.625</v>
       </c>
       <c r="N25" s="233">
         <f>SUM(N16:N24)</f>
-        <v>2989.8305084745757</v>
+        <v>3538.983050847457</v>
       </c>
       <c r="O25" s="101">
         <f>SUM(O16:O24)</f>
-        <v>84.949997542372884</v>
+        <v>100.55304025423729</v>
       </c>
       <c r="P25" s="234">
         <f>SUM(P16:P24)</f>
-        <v>17074.94950601695</v>
+        <v>20211.161091101698</v>
       </c>
       <c r="Q25" s="239">
         <f>SUM(Q16:Q24)</f>
@@ -62415,7 +62415,7 @@
       <c r="O28" s="369"/>
       <c r="P28" s="139">
         <f>I25</f>
-        <v>15819.400000000001</v>
+        <v>18725</v>
       </c>
     </row>
     <row r="29" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -62436,7 +62436,7 @@
       <c r="O29" s="371"/>
       <c r="P29" s="140">
         <f>+J25</f>
-        <v>1265.5520000000001</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="30" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -62457,7 +62457,7 @@
       <c r="O30" s="371"/>
       <c r="P30" s="140">
         <f>+K25+L25</f>
-        <v>553.67900000000009</v>
+        <v>655.37500000000011</v>
       </c>
     </row>
     <row r="31" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -62479,7 +62479,7 @@
       <c r="O31" s="371"/>
       <c r="P31" s="140">
         <f>P28-P29-P30</f>
-        <v>14000.169000000002</v>
+        <v>16571.625</v>
       </c>
     </row>
     <row r="32" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -62503,7 +62503,7 @@
       </c>
       <c r="P32" s="140">
         <f>+N25</f>
-        <v>2989.8305084745757</v>
+        <v>3538.983050847457</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -62525,7 +62525,7 @@
       <c r="O33" s="373"/>
       <c r="P33" s="140">
         <f>P31+P32</f>
-        <v>16989.999508474579</v>
+        <v>20110.608050847455</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -62550,7 +62550,7 @@
       </c>
       <c r="P34" s="140">
         <f>O34*P33</f>
-        <v>84.949997542372898</v>
+        <v>100.55304025423727</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -62560,7 +62560,7 @@
       <c r="O35" s="375"/>
       <c r="P35" s="297">
         <f>+P33+P34</f>
-        <v>17074.94950601695</v>
+        <v>20211.161091101694</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -62647,7 +62647,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="88" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="10" orientation="landscape" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="1">
